--- a/Data/EXCEL/Transfer/salemon/20240711/6841-salemon-20240711.xlsx
+++ b/Data/EXCEL/Transfer/salemon/20240711/6841-salemon-20240711.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlsx\20240711\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\GithubProjects\GoodinfoData2DB\Data\EXCEL\Transfer\salemon\20240711\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3B5154FC-346B-4A81-A491-9E6AADFCB051}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{385601E1-8640-465D-AF9A-A498F66CFAD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="900" yWindow="290" windowWidth="18240" windowHeight="13390" xr2:uid="{33ABA906-ACA7-4260-BBDC-417DAF693993}"/>
+    <workbookView xWindow="768" yWindow="684" windowWidth="20004" windowHeight="13956" xr2:uid="{79941104-11B1-47E8-A97C-7F120A55DB75}"/>
   </bookViews>
   <sheets>
     <sheet name="6841-salemon-20240711" sheetId="2" r:id="rId1"/>
@@ -1261,22 +1261,22 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B3DA1F8-FAA3-4F59-83C2-99A7CCE49C6A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E66D39C8-D3E8-4A83-8A34-15F0C2829CA7}">
   <dimension ref="A1:Q81"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="5" width="5.36328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.08984375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.90625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.1796875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.36328125" bestFit="1" customWidth="1"/>
-    <col min="10" max="13" width="6.1796875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="5.36328125" bestFit="1" customWidth="1"/>
-    <col min="15" max="17" width="6.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="5" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="10" max="13" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="15" max="17" width="6.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
@@ -1303,7 +1303,7 @@
       <c r="P1" s="19"/>
       <c r="Q1" s="20"/>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" s="16"/>
       <c r="B2" s="15" t="s">
         <v>4</v>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" s="16"/>
       <c r="B3" s="16"/>
       <c r="C3" s="16"/>
@@ -1385,7 +1385,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" s="17"/>
       <c r="B4" s="17"/>
       <c r="C4" s="17"/>
@@ -1424,7 +1424,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
         <v>45444</v>
       </c>
@@ -1477,7 +1477,7 @@
         <v>415.8</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" s="10">
         <v>45413</v>
       </c>
@@ -1530,7 +1530,7 @@
         <v>432.5</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>45383</v>
       </c>
@@ -1583,7 +1583,7 @@
         <v>364.8</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" s="10">
         <v>45352</v>
       </c>
@@ -1636,7 +1636,7 @@
         <v>342.4</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
         <v>45323</v>
       </c>
@@ -1689,7 +1689,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10" s="10">
         <v>45292</v>
       </c>
@@ -1742,7 +1742,7 @@
         <v>175.6</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" s="5">
         <v>45261</v>
       </c>
@@ -1795,7 +1795,7 @@
         <v>72.8</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12" s="10">
         <v>45231</v>
       </c>
@@ -1848,7 +1848,7 @@
         <v>79.900000000000006</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A13" s="5">
         <v>45200</v>
       </c>
@@ -1901,7 +1901,7 @@
         <v>58.3</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A14" s="10">
         <v>45170</v>
       </c>
@@ -1954,7 +1954,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A15" s="5">
         <v>45139</v>
       </c>
@@ -2007,7 +2007,7 @@
         <v>36.5</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A16" s="10">
         <v>45108</v>
       </c>
@@ -2060,7 +2060,7 @@
         <v>35.200000000000003</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A17" s="5">
         <v>45078</v>
       </c>
@@ -2113,7 +2113,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A18" s="10">
         <v>45047</v>
       </c>
@@ -2166,7 +2166,7 @@
         <v>47.7</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A19" s="5">
         <v>45017</v>
       </c>
@@ -2219,7 +2219,7 @@
         <v>50.9</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A20" s="10">
         <v>44986</v>
       </c>
@@ -2272,7 +2272,7 @@
         <v>35.299999999999997</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A21" s="5">
         <v>44958</v>
       </c>
@@ -2325,7 +2325,7 @@
         <v>79.599999999999994</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A22" s="10">
         <v>44927</v>
       </c>
@@ -2378,7 +2378,7 @@
         <v>239.5</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A23" s="5">
         <v>44896</v>
       </c>
@@ -2431,7 +2431,7 @@
         <v>40.9</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A24" s="10">
         <v>44866</v>
       </c>
@@ -2484,7 +2484,7 @@
         <v>15.7</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A25" s="5">
         <v>44835</v>
       </c>
@@ -2537,7 +2537,7 @@
         <v>8.76</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A26" s="10">
         <v>44805</v>
       </c>
@@ -2590,7 +2590,7 @@
         <v>-3.19</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A27" s="5">
         <v>44774</v>
       </c>
@@ -2643,7 +2643,7 @@
         <v>-2.8</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A28" s="10">
         <v>44743</v>
       </c>
@@ -2696,7 +2696,7 @@
         <v>-14.4</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A29" s="5">
         <v>44713</v>
       </c>
@@ -2749,7 +2749,7 @@
         <v>-19.7</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A30" s="10">
         <v>44682</v>
       </c>
@@ -2802,7 +2802,7 @@
         <v>-48.8</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A31" s="5">
         <v>44652</v>
       </c>
@@ -2855,7 +2855,7 @@
         <v>-60</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A32" s="10">
         <v>44621</v>
       </c>
@@ -2908,7 +2908,7 @@
         <v>-67.8</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A33" s="5">
         <v>44593</v>
       </c>
@@ -2961,7 +2961,7 @@
         <v>1579.8</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A34" s="10">
         <v>44562</v>
       </c>
@@ -3014,7 +3014,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A35" s="5">
         <v>44531</v>
       </c>
@@ -3067,7 +3067,7 @@
         <v>996.8</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A36" s="10">
         <v>44501</v>
       </c>
@@ -3120,7 +3120,7 @@
         <v>1011.3</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A37" s="5">
         <v>44470</v>
       </c>
@@ -3173,7 +3173,7 @@
         <v>1015.9</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A38" s="10">
         <v>44440</v>
       </c>
@@ -3226,7 +3226,7 @@
         <v>1012.2</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A39" s="5">
         <v>44409</v>
       </c>
@@ -3279,7 +3279,7 @@
         <v>917.5</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A40" s="10">
         <v>44378</v>
       </c>
@@ -3332,7 +3332,7 @@
         <v>893.4</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A41" s="5">
         <v>44348</v>
       </c>
@@ -3385,202 +3385,202 @@
         <v>896</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A42" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A43" s="5">
         <v>45444</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A44" s="10">
         <v>45413</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A45" s="5">
         <v>45383</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A46" s="10">
         <v>45352</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A47" s="5">
         <v>45323</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A48" s="10">
         <v>45292</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A49" s="5">
         <v>45261</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A50" s="10">
         <v>45231</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A51" s="5">
         <v>45200</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A52" s="10">
         <v>45170</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A53" s="5">
         <v>45139</v>
       </c>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A54" s="10">
         <v>45108</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A55" s="5">
         <v>45078</v>
       </c>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A56" s="10">
         <v>45047</v>
       </c>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A57" s="5">
         <v>45017</v>
       </c>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A58" s="10">
         <v>44986</v>
       </c>
     </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A59" s="5">
         <v>44958</v>
       </c>
     </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A60" s="10">
         <v>44927</v>
       </c>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A61" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A62" s="5">
         <v>44896</v>
       </c>
     </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A63" s="10">
         <v>44866</v>
       </c>
     </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A64" s="5">
         <v>44835</v>
       </c>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A65" s="10">
         <v>44805</v>
       </c>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A66" s="5">
         <v>44774</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A67" s="10">
         <v>44743</v>
       </c>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A68" s="5">
         <v>44713</v>
       </c>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A69" s="10">
         <v>44682</v>
       </c>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A70" s="5">
         <v>44652</v>
       </c>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A71" s="10">
         <v>44621</v>
       </c>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A72" s="5">
         <v>44593</v>
       </c>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A73" s="10">
         <v>44562</v>
       </c>
     </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A74" s="5">
         <v>44531</v>
       </c>
     </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A75" s="10">
         <v>44501</v>
       </c>
     </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A76" s="5">
         <v>44470</v>
       </c>
     </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A77" s="10">
         <v>44440</v>
       </c>
     </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A78" s="5">
         <v>44409</v>
       </c>
     </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A79" s="10">
         <v>44378</v>
       </c>
     </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A80" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A81" s="5">
         <v>44348</v>
       </c>
